--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487155_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487155_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.9956</v>
+        <v>2.6581</v>
       </c>
       <c r="E2" t="n">
-        <v>1.4696</v>
+        <v>0.8280999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5261</v>
+        <v>1.8301</v>
       </c>
       <c r="G2" t="n">
         <v>1.6262</v>
@@ -610,13 +610,13 @@
         <v>1.5441</v>
       </c>
       <c r="S2" t="n">
-        <v>2.7748</v>
+        <v>1.4373</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.2905</v>
       </c>
       <c r="U2" t="n">
-        <v>1.8428</v>
+        <v>1.1468</v>
       </c>
       <c r="V2" t="n">
         <v>-0.9843</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. OLIVEIRA GETE</t>
+          <t>E. MARTINEZ CENDON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3123</v>
+        <v>2.5365</v>
       </c>
       <c r="E3" t="n">
-        <v>2.302</v>
+        <v>2.1841</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0103</v>
+        <v>0.3524</v>
       </c>
       <c r="G3" t="n">
-        <v>1.0489</v>
+        <v>2.6757</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.6883</v>
+        <v>2.5408</v>
       </c>
       <c r="I3" t="n">
-        <v>1.7372</v>
+        <v>0.135</v>
       </c>
       <c r="J3" t="n">
-        <v>2.3102</v>
+        <v>3.1225</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4138</v>
+        <v>3.2289</v>
       </c>
       <c r="L3" t="n">
-        <v>1.8964</v>
+        <v>-0.1064</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.2613</v>
+        <v>-0.4468</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.1021</v>
+        <v>-0.6881</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1592</v>
+        <v>0.2413</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.3511</v>
+        <v>-0.965</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.8951</v>
+        <v>-1.9301</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5441</v>
+        <v>0.965</v>
       </c>
       <c r="S3" t="n">
-        <v>2.9771</v>
+        <v>0.2118</v>
       </c>
       <c r="T3" t="n">
-        <v>2.0293</v>
+        <v>-0.2363</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9478</v>
+        <v>0.4481</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6374</v>
+        <v>0.614</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8576</v>
+        <v>1.228</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2202</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. MARTINEZ CENDON</t>
+          <t>A. OLIVEIRA GETE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5619</v>
+        <v>1.6079</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4236</v>
+        <v>0.9189000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1383</v>
+        <v>0.6891</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6757</v>
+        <v>1.0489</v>
       </c>
       <c r="H4" t="n">
-        <v>2.5408</v>
+        <v>-0.6883</v>
       </c>
       <c r="I4" t="n">
-        <v>0.135</v>
+        <v>1.7372</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1225</v>
+        <v>2.3102</v>
       </c>
       <c r="K4" t="n">
-        <v>3.2289</v>
+        <v>0.4138</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.1064</v>
+        <v>1.8964</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4468</v>
+        <v>-1.2613</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6881</v>
+        <v>-1.1021</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2413</v>
+        <v>-0.1592</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.965</v>
+        <v>-1.3511</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9301</v>
+        <v>-2.8951</v>
       </c>
       <c r="R4" t="n">
-        <v>0.965</v>
+        <v>1.5441</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7628</v>
+        <v>1.2727</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9967</v>
+        <v>0.6462</v>
       </c>
       <c r="U4" t="n">
-        <v>0.234</v>
+        <v>0.6266</v>
       </c>
       <c r="V4" t="n">
-        <v>0.614</v>
+        <v>0.6374</v>
       </c>
       <c r="W4" t="n">
-        <v>1.228</v>
+        <v>0.8576</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.614</v>
+        <v>-0.2202</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. EGAA AYERZA</t>
+          <t>A. EGUSKITZA AGINALDE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7144</v>
+        <v>1.0778</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2874</v>
+        <v>0.8859</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.573</v>
+        <v>0.1919</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.049</v>
+        <v>0.7593</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.4574</v>
+        <v>0.383</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4084</v>
+        <v>0.3763</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3323</v>
+        <v>1.2399</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1035</v>
+        <v>1.1178</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2288</v>
+        <v>0.1221</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.3813</v>
+        <v>-0.4805</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5609</v>
+        <v>-0.7347</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8204</v>
+        <v>0.2542</v>
       </c>
       <c r="P5" t="n">
-        <v>0.579</v>
+        <v>0.772</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.579</v>
+        <v>0.772</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1844</v>
+        <v>-0.2333</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0449</v>
+        <v>-0.3539</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2294</v>
+        <v>0.1206</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.2202</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.2202</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. EGUSKITZA AGINALDE</t>
+          <t>J. EGAA AYERZA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6375999999999999</v>
+        <v>0.8344</v>
       </c>
       <c r="E6" t="n">
-        <v>0.526</v>
+        <v>1.4877</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1116</v>
+        <v>-0.6533</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7593</v>
+        <v>-0.049</v>
       </c>
       <c r="H6" t="n">
-        <v>0.383</v>
+        <v>-0.4574</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3763</v>
+        <v>0.4084</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2399</v>
+        <v>1.3323</v>
       </c>
       <c r="K6" t="n">
-        <v>1.1178</v>
+        <v>0.1035</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1221</v>
+        <v>1.2288</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4805</v>
+        <v>-1.3813</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7347</v>
+        <v>-0.5609</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2542</v>
+        <v>-0.8204</v>
       </c>
       <c r="P6" t="n">
-        <v>0.772</v>
+        <v>0.579</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.772</v>
+        <v>0.579</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6736</v>
+        <v>0.3044</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7139</v>
+        <v>0.1553</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0403</v>
+        <v>0.149</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2202</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2202</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. ZUBIZARRETA ALBIZU</t>
+          <t>M. LARRAÑAGA ORMAZABAL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.061</v>
+        <v>0.2157</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7619</v>
+        <v>-0.6198</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8229</v>
+        <v>0.8355</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.3544</v>
+        <v>0.3503</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.5722</v>
+        <v>-0.5029</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2178</v>
+        <v>0.8532</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5144</v>
+        <v>0.5772</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6574</v>
+        <v>0.5122</v>
       </c>
       <c r="L7" t="n">
-        <v>1.1717</v>
+        <v>0.065</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.8688</v>
+        <v>-0.2269</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9149</v>
+        <v>-1.0152</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9539</v>
+        <v>0.7883</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.7371</v>
+        <v>-0.193</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.8951</v>
+        <v>-0.965</v>
       </c>
       <c r="R7" t="n">
-        <v>1.158</v>
+        <v>0.772</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1051</v>
+        <v>-0.0073</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0727</v>
+        <v>-0.232</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1778</v>
+        <v>0.2247</v>
       </c>
       <c r="V7" t="n">
-        <v>3.1355</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>3.0699</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0.06560000000000001</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. LARRAÑAGA ORMAZABAL</t>
+          <t>M. ZUBIZARRETA ALBIZU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.873</v>
+        <v>0.1918</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2801</v>
+        <v>0.8809</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4071</v>
+        <v>-0.6891</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3503</v>
+        <v>-1.3544</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5029</v>
+        <v>-1.5722</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8532</v>
+        <v>0.2178</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5772</v>
+        <v>0.5144</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5122</v>
+        <v>-0.6574</v>
       </c>
       <c r="L8" t="n">
-        <v>0.065</v>
+        <v>1.1717</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2269</v>
+        <v>-1.8688</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.0152</v>
+        <v>-0.9149</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7883</v>
+        <v>-0.9539</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.193</v>
+        <v>-1.7371</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.965</v>
+        <v>-2.8951</v>
       </c>
       <c r="R8" t="n">
-        <v>0.772</v>
+        <v>1.158</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0959</v>
+        <v>0.1477</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8923</v>
+        <v>0.1917</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2036</v>
+        <v>-0.044</v>
       </c>
       <c r="V8" t="n">
-        <v>0.06560000000000001</v>
+        <v>3.1355</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>3.0699</v>
       </c>
       <c r="X8" t="n">
         <v>0.06560000000000001</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. ZABALETA LASA</t>
+          <t>A. BOZAL GOMEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.4289</v>
+        <v>-1.8853</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7093</v>
+        <v>-0.8925999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.7196</v>
+        <v>-0.9927</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.4233</v>
+        <v>-2.6084</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.5629</v>
+        <v>0.7731</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.8604</v>
+        <v>-3.3816</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.1667</v>
+        <v>-0.5198</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6212</v>
+        <v>1.3609</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5455</v>
+        <v>-1.8807</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.2566</v>
+        <v>-2.0886</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9417</v>
+        <v>-0.5878</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.3149</v>
+        <v>-1.5009</v>
       </c>
       <c r="P9" t="n">
-        <v>1.3511</v>
+        <v>0.386</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R9" t="n">
         <v>1.3511</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5777</v>
+        <v>0.0512</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4574</v>
+        <v>0.0205</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1203</v>
+        <v>0.0307</v>
       </c>
       <c r="V9" t="n">
-        <v>0.06560000000000001</v>
+        <v>0.2859</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.5717</v>
       </c>
       <c r="X9" t="n">
-        <v>0.06560000000000001</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. BOZAL GOMEZ</t>
+          <t>A. ZABALETA LASA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.6735</v>
+        <v>-2.6103</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4934</v>
+        <v>-0.8907</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1801</v>
+        <v>-1.7196</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.6084</v>
+        <v>-4.4233</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7731</v>
+        <v>-1.5629</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.3816</v>
+        <v>-2.8604</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.5198</v>
+        <v>-1.1667</v>
       </c>
       <c r="K10" t="n">
-        <v>1.3609</v>
+        <v>-0.6212</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.8807</v>
+        <v>-0.5455</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.0886</v>
+        <v>-3.2566</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5878</v>
+        <v>-0.9417</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.5009</v>
+        <v>-2.3149</v>
       </c>
       <c r="P10" t="n">
-        <v>0.386</v>
+        <v>1.3511</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>1.3511</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.737</v>
+        <v>0.3963</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5803</v>
+        <v>0.276</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1567</v>
+        <v>0.1203</v>
       </c>
       <c r="V10" t="n">
-        <v>0.2859</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="W10" t="n">
-        <v>0.5717</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2859</v>
+        <v>0.06560000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.1813</v>
+        <v>-3.0276</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7092</v>
+        <v>-1.6091</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4721</v>
+        <v>-1.4185</v>
       </c>
       <c r="G11" t="n">
         <v>-2.7307</v>
@@ -1312,13 +1312,13 @@
         <v>0.579</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1983</v>
+        <v>0.352</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0873</v>
+        <v>0.1874</v>
       </c>
       <c r="U11" t="n">
-        <v>0.111</v>
+        <v>0.1646</v>
       </c>
       <c r="V11" t="n">
         <v>-1.228</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.0041</v>
+        <v>1.599</v>
       </c>
       <c r="E12" t="n">
-        <v>2.5785</v>
+        <v>3.173400000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.5743</v>
+        <v>-1.5742</v>
       </c>
       <c r="G12" t="n">
         <v>-4.705400000000001</v>
@@ -1363,25 +1363,25 @@
         <v>-2.7026</v>
       </c>
       <c r="J12" t="n">
-        <v>6.872400000000001</v>
+        <v>6.872399999999999</v>
       </c>
       <c r="K12" t="n">
         <v>6.0119</v>
       </c>
       <c r="L12" t="n">
-        <v>0.8603999999999996</v>
+        <v>0.8604000000000001</v>
       </c>
       <c r="M12" t="n">
         <v>-11.5777</v>
       </c>
       <c r="N12" t="n">
-        <v>-8.014799999999999</v>
+        <v>-8.014800000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>-3.563000000000001</v>
+        <v>-3.563</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.0001000000000003221</v>
+        <v>-0.000100000000000211</v>
       </c>
       <c r="Q12" t="n">
         <v>-10.6153</v>
@@ -1390,16 +1390,16 @@
         <v>10.6154</v>
       </c>
       <c r="S12" t="n">
-        <v>3.3379</v>
+        <v>3.9328</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3505999999999999</v>
+        <v>0.9454</v>
       </c>
       <c r="U12" t="n">
-        <v>2.9875</v>
+        <v>2.9874</v>
       </c>
       <c r="V12" t="n">
-        <v>2.3715</v>
+        <v>2.371499999999999</v>
       </c>
       <c r="W12" t="n">
         <v>5.970800000000001</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.18</v>
+        <v>5.1529</v>
       </c>
       <c r="E13" t="n">
         <v>4.2885</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8914</v>
+        <v>0.8643</v>
       </c>
       <c r="G13" t="n">
         <v>0.9301</v>
@@ -1468,13 +1468,13 @@
         <v>1.9301</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1362</v>
+        <v>-0.1633</v>
       </c>
       <c r="T13" t="n">
         <v>-0.538</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4018</v>
+        <v>0.3747</v>
       </c>
       <c r="V13" t="n">
         <v>2.4559</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.9308</v>
+        <v>4.5988</v>
       </c>
       <c r="E14" t="n">
-        <v>2.8505</v>
+        <v>3.2511</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0803</v>
+        <v>1.3477</v>
       </c>
       <c r="G14" t="n">
         <v>4.6366</v>
@@ -1546,13 +1546,13 @@
         <v>1.158</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8758</v>
+        <v>-0.2079</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9227</v>
+        <v>-0.5221</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0469</v>
+        <v>0.3143</v>
       </c>
       <c r="V14" t="n">
         <v>0.9421</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>N. NDOYE</t>
+          <t>D. KEITH CAMARA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.1529</v>
+        <v>1.9828</v>
       </c>
       <c r="E15" t="n">
-        <v>3.9934</v>
+        <v>0.6753</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.8405</v>
+        <v>1.3075</v>
       </c>
       <c r="G15" t="n">
-        <v>0.422</v>
+        <v>1.7175</v>
       </c>
       <c r="H15" t="n">
-        <v>1.9343</v>
+        <v>0.8985</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.5123</v>
+        <v>0.819</v>
       </c>
       <c r="J15" t="n">
-        <v>3.0716</v>
+        <v>0.7695</v>
       </c>
       <c r="K15" t="n">
-        <v>3.6171</v>
+        <v>0.7452</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5455</v>
+        <v>0.0243</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.6496</v>
+        <v>0.948</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.6828</v>
+        <v>0.1533</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.9668</v>
+        <v>0.7947</v>
       </c>
       <c r="P15" t="n">
-        <v>1.158</v>
+        <v>0.386</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.158</v>
+        <v>0.386</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2869</v>
+        <v>-0.4488</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6359</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.349</v>
+        <v>-0.3546</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2859</v>
+        <v>0.3281</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>0.3281</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. KEITH CAMARA</t>
+          <t>N. NDOYE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8017</v>
+        <v>1.5054</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9757</v>
+        <v>3.2924</v>
       </c>
       <c r="F16" t="n">
-        <v>0.826</v>
+        <v>-1.787</v>
       </c>
       <c r="G16" t="n">
-        <v>1.7175</v>
+        <v>0.422</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8985</v>
+        <v>1.9343</v>
       </c>
       <c r="I16" t="n">
-        <v>0.819</v>
+        <v>-1.5123</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7695</v>
+        <v>3.0716</v>
       </c>
       <c r="K16" t="n">
-        <v>0.7452</v>
+        <v>3.6171</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0243</v>
+        <v>-0.5455</v>
       </c>
       <c r="M16" t="n">
-        <v>0.948</v>
+        <v>-2.6496</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1533</v>
+        <v>-1.6828</v>
       </c>
       <c r="O16" t="n">
-        <v>0.7947</v>
+        <v>-0.9668</v>
       </c>
       <c r="P16" t="n">
-        <v>0.386</v>
+        <v>1.158</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.386</v>
+        <v>1.158</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6299</v>
+        <v>-0.3606</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2062</v>
+        <v>-0.06510000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8362000000000001</v>
+        <v>-0.2955</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3281</v>
+        <v>0.2859</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3281</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>O. HERNANDEZ HERNANDEZ</t>
+          <t>A. GARCIA NAVALON</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3289</v>
+        <v>0.0959</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.7323</v>
+        <v>-1.5107</v>
       </c>
       <c r="F17" t="n">
-        <v>2.4034</v>
+        <v>1.6066</v>
       </c>
       <c r="G17" t="n">
-        <v>2.3128</v>
+        <v>-1.1107</v>
       </c>
       <c r="H17" t="n">
-        <v>1.9023</v>
+        <v>-1.2492</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4105</v>
+        <v>0.1385</v>
       </c>
       <c r="J17" t="n">
-        <v>1.4512</v>
+        <v>-1.1713</v>
       </c>
       <c r="K17" t="n">
-        <v>1.2884</v>
+        <v>-1.1955</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1628</v>
+        <v>0.0243</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8617</v>
+        <v>0.0605</v>
       </c>
       <c r="N17" t="n">
-        <v>0.6139</v>
+        <v>-0.0537</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2478</v>
+        <v>0.1142</v>
       </c>
       <c r="P17" t="n">
-        <v>-3.8602</v>
+        <v>1.5441</v>
       </c>
       <c r="Q17" t="n">
-        <v>-4.8252</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.965</v>
+        <v>1.5441</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8903</v>
+        <v>-0.3374</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0278</v>
+        <v>-0.3394</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8625</v>
+        <v>0.002</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3281</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.614</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. GARCIA NAVALON</t>
+          <t>D. LAMAZARES ABASCAL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3916</v>
+        <v>-0.5589</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.8111</v>
+        <v>-0.7944</v>
       </c>
       <c r="F18" t="n">
-        <v>1.4195</v>
+        <v>0.2354</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.1107</v>
+        <v>0.7363</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.2492</v>
+        <v>0.295</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1385</v>
+        <v>0.4413</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.1713</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.1955</v>
+        <v>0.0414</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0243</v>
+        <v>0.0407</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0605</v>
+        <v>0.6542</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0537</v>
+        <v>0.2536</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1142</v>
+        <v>0.4006</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5441</v>
+        <v>-0.965</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5441</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8249</v>
+        <v>-0.0443</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6398</v>
+        <v>0.0886</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1851</v>
+        <v>-0.1329</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. LAMAZARES ABASCAL</t>
+          <t>O. HERNANDEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7195</v>
+        <v>-1.058</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.7944</v>
+        <v>-3.0327</v>
       </c>
       <c r="F19" t="n">
-        <v>0.07480000000000001</v>
+        <v>1.9747</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7363</v>
+        <v>2.3128</v>
       </c>
       <c r="H19" t="n">
-        <v>0.295</v>
+        <v>1.9023</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4413</v>
+        <v>0.4105</v>
       </c>
       <c r="J19" t="n">
-        <v>0.08210000000000001</v>
+        <v>1.4512</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0414</v>
+        <v>1.2884</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0407</v>
+        <v>0.1628</v>
       </c>
       <c r="M19" t="n">
-        <v>0.6542</v>
+        <v>0.8617</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2536</v>
+        <v>0.6139</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4006</v>
+        <v>0.2478</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.965</v>
+        <v>-3.8602</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.965</v>
+        <v>-4.8252</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>0.965</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2049</v>
+        <v>0.1613</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0886</v>
+        <v>-0.2726</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2935</v>
+        <v>0.4339</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.2859</v>
+        <v>0.3281</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.614</v>
       </c>
       <c r="X19" t="n">
         <v>-0.2859</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.0699</v>
+        <v>-2.9033</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8335</v>
+        <v>-0.533</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.2364</v>
+        <v>-2.3702</v>
       </c>
       <c r="G21" t="n">
         <v>-1.1341</v>
@@ -2092,13 +2092,13 @@
         <v>1.9301</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4449</v>
+        <v>-0.2783</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8632</v>
+        <v>-0.5628</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4184</v>
+        <v>0.2845</v>
       </c>
       <c r="V21" t="n">
         <v>-2.4559</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.1647</v>
+        <v>-6.7572</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.4447</v>
+        <v>-4.1443</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.72</v>
+        <v>-2.6129</v>
       </c>
       <c r="G22" t="n">
         <v>-3.2668</v>
@@ -2170,13 +2170,13 @@
         <v>1.3511</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1911</v>
+        <v>-0.7836</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9822</v>
+        <v>-0.6818</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2089</v>
+        <v>-0.1018</v>
       </c>
       <c r="V22" t="n">
         <v>-2.1278</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.004</v>
+        <v>-0.336400000000002</v>
       </c>
       <c r="E23" t="n">
-        <v>1.5742</v>
+        <v>1.5743</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.5784</v>
+        <v>-1.9108</v>
       </c>
       <c r="G23" t="n">
         <v>4.705400000000001</v>
@@ -2248,13 +2248,13 @@
         <v>10.6154</v>
       </c>
       <c r="S23" t="n">
-        <v>-3.3381</v>
+        <v>-2.6705</v>
       </c>
       <c r="T23" t="n">
         <v>-2.9874</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3507</v>
+        <v>0.3170000000000001</v>
       </c>
       <c r="V23" t="n">
         <v>-2.3715</v>
